--- a/CCD-Bench/CCD-Bench_Business_V2.xlsx
+++ b/CCD-Bench/CCD-Bench_Business_V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data Storage\POLIMI\Semester 2\Multidisciplinary Project\LLM Culture Map Project\Code\CCD-Bench\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E311A65E-86C3-483B-9A20-5F3283C40E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BD2902-E38D-4982-8F42-3AD103E4D772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
